--- a/content/day05/data/test_cases.xlsx
+++ b/content/day05/data/test_cases.xlsx
@@ -1,165 +1,69 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\16531\Desktop\selenium-learning\content\day05\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1934A502-AFAC-49BA-BFAC-1E945727F8D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
-  <si>
-    <t>case_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>case_name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>keyword</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>expected_result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>actul_result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>status</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>remark</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TC001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TC002</t>
-  </si>
-  <si>
-    <t>TC003</t>
-  </si>
-  <si>
-    <t>TC004</t>
-  </si>
-  <si>
-    <t>搜索追觅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>追觅科技</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>追觅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>搜索Selenium</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Selenium</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>搜索Python</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Python</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>搜索错误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">xxxxxxxxxx	</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>找不到</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TC005</t>
-  </si>
-  <si>
-    <t>搜索美女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>美女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <color theme="1"/>
-      <name val="黑体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -174,31 +78,90 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -464,114 +427,420 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
-    <col min="6" max="7" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col width="12" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="15.21875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="12" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="24.6640625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="20.44140625" customWidth="1" min="5" max="5"/>
+    <col width="10.44140625" bestFit="1" customWidth="1" min="6" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>23</v>
+    <row r="1" ht="17.4" customFormat="1" customHeight="1" s="1" thickBot="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>case_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>expected</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.4" customFormat="1" customHeight="1" s="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TC002</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>搜索Selenium</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="14.4" customFormat="1" customHeight="1" s="2">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>TC003</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>搜索Python</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.4" customFormat="1" customHeight="1" s="2">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TC004</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>搜索错误</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xxxxxxxxxx	</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>找不到</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14.4" customFormat="1" customHeight="1" s="2">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TC005</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>搜索美女</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>美女</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>美女</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="14.4" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TC002</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>搜索Selenium</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>实际标题包含期望值</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TC003</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>搜索Python</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>实际标题包含期望值</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TC004</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>搜索错误</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xxxxxxxxxx	</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>找不到</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>实际值是xxxxxxxxxx_百度搜索,期望值是找不到</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TC004</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>搜索错误</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xxxxxxxxxx	</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>找不到</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>实际值是xxxxxxxxxx_百度搜索,期望值是找不到
+assert 'Fail' == 'Pass'
+  - Pass
+  + Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TC005</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>搜索美女</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>美女</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>美女</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>实际标题包含期望值</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="1200" verticalDpi="1200"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
+  <sheetData>
+    <row r="1" ht="14.4" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>TC002</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>搜索Selenium</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.4" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TC003</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>搜索Python</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14.4" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>TC004</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>搜索错误</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xxxxxxxxxx	</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>找不到</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.4" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TC005</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>搜索美女</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>美女</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>美女</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/content/day05/data/test_cases.xlsx
+++ b/content/day05/data/test_cases.xlsx
@@ -40,30 +40,12 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -78,17 +60,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -432,7 +408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="12" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -443,7 +419,7 @@
     <col width="10.44140625" bestFit="1" customWidth="1" min="6" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.4" customFormat="1" customHeight="1" s="1" thickBot="1">
+    <row r="1" ht="17.4" customHeight="1" thickBot="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>case_id</t>
@@ -480,90 +456,89 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="14.4" customFormat="1" customHeight="1" s="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="14.4" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TC001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>搜索Selenium</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14.4" customHeight="1">
+      <c r="A3" t="inlineStr">
         <is>
           <t>TC002</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>搜索Selenium</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Selenium</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Selenium</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="14.4" customFormat="1" customHeight="1" s="2">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>搜索Python</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.4" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TC003</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>搜索Python</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="14.4" customFormat="1" customHeight="1" s="2">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>搜索错误</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xxxxxxxxxx	</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>找不到</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14.4" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>TC004</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>搜索错误</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">xxxxxxxxxx	</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>找不到</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="14.4" customFormat="1" customHeight="1" s="2">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TC005</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>搜索美女</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>美女</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>美女</t>
         </is>
@@ -572,7 +547,7 @@
     <row r="6" ht="14.4" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TC002</t>
+          <t>TC001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,23 +563,13 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>Selenium</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>实际标题包含期望值</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TC003</t>
+          <t>TC002</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -620,23 +585,13 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>实际标题包含期望值</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TC004</t>
+          <t>TC003</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -652,16 +607,6 @@
       <c r="D8" t="inlineStr">
         <is>
           <t>找不到</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>实际值是xxxxxxxxxx_百度搜索,期望值是找不到</t>
         </is>
       </c>
     </row>
@@ -673,67 +618,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>搜索错误</t>
+          <t>搜索美女</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">xxxxxxxxxx	</t>
+          <t>美女</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>找不到</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>实际值是xxxxxxxxxx_百度搜索,期望值是找不到
-assert 'Fail' == 'Pass'
-  - Pass
-  + Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TC005</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>搜索美女</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
           <t>美女</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>美女</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>实际标题包含期望值</t>
         </is>
       </c>
     </row>
@@ -753,88 +648,88 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <sheetData>
     <row r="1" ht="14.4" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TC002</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>搜索Selenium</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Selenium</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Selenium</t>
         </is>
       </c>
     </row>
     <row r="2" ht="14.4" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>TC003</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>搜索Python</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
     </row>
     <row r="3" ht="14.4" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>TC004</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>搜索错误</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">xxxxxxxxxx	</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>找不到</t>
         </is>
       </c>
     </row>
     <row r="4" ht="14.4" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>TC005</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>搜索美女</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>美女</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>美女</t>
         </is>
